--- a/test-results/excel-reports/stage_report_2026-05-07.xlsx
+++ b/test-results/excel-reports/stage_report_2026-05-07.xlsx
@@ -63,7 +63,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>52.16</t>
+    <t>51.70</t>
   </si>
   <si>
     <t>tests\ui\regressionTest.stage.spec.ts</t>
@@ -72,7 +72,7 @@
     <t/>
   </si>
   <si>
-    <t>2026-05-07T09:03:54.250Z</t>
+    <t>2026-05-07T09:18:19.215Z</t>
   </si>
   <si>
     <t>STAGE</t>
@@ -90,7 +90,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>5/7/2026, 3:03:54 PM</t>
+    <t>5/7/2026, 3:18:19 PM</t>
   </si>
   <si>
     <t>Total Tests</t>
@@ -126,7 +126,7 @@
     <t>Avg Duration (ms)</t>
   </si>
   <si>
-    <t>52162.00</t>
+    <t>51698.00</t>
   </si>
   <si>
     <t>passed</t>
@@ -629,7 +629,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="2">
-        <v>52162</v>
+        <v>51698</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>16</v>

--- a/test-results/excel-reports/stage_report_2026-05-07.xlsx
+++ b/test-results/excel-reports/stage_report_2026-05-07.xlsx
@@ -63,7 +63,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>51.70</t>
+    <t>55.60</t>
   </si>
   <si>
     <t>tests\ui\regressionTest.stage.spec.ts</t>
@@ -72,7 +72,7 @@
     <t/>
   </si>
   <si>
-    <t>2026-05-07T09:18:19.215Z</t>
+    <t>2026-05-07T19:11:30.106Z</t>
   </si>
   <si>
     <t>STAGE</t>
@@ -90,7 +90,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>5/7/2026, 3:18:19 PM</t>
+    <t>5/8/2026, 1:11:30 AM</t>
   </si>
   <si>
     <t>Total Tests</t>
@@ -126,7 +126,7 @@
     <t>Avg Duration (ms)</t>
   </si>
   <si>
-    <t>51698.00</t>
+    <t>55602.00</t>
   </si>
   <si>
     <t>passed</t>
@@ -629,7 +629,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="2">
-        <v>51698</v>
+        <v>55602</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>16</v>
